--- a/Live_List.xlsx
+++ b/Live_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\675939\Documents\PRIVATE\SensuCarens\website_sozai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B23CDF-C23B-4122-A618-F3AF31EE717A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F98E34-A483-43EB-AB10-A754339CB729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1150" yWindow="1280" windowWidth="14400" windowHeight="8170" xr2:uid="{669D6A52-F58A-48A4-ACC6-46AD3FC492BB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{669D6A52-F58A-48A4-ACC6-46AD3FC492BB}"/>
   </bookViews>
   <sheets>
     <sheet name="LIVE" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>場所</t>
     <rPh sb="0" eb="2">
@@ -52,18 +52,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>備考</t>
-    <rPh sb="0" eb="2">
-      <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>open</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>close</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -199,6 +188,10 @@
     <rPh sb="19" eb="21">
       <t>シンジュク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>start</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -635,46 +628,43 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -682,25 +672,25 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>24</v>
       </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
       </c>
       <c r="I2" s="4">
         <v>0.72916666666666663</v>
@@ -715,10 +705,10 @@
         <v>3000</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -726,25 +716,25 @@
         <v>2016</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
       </c>
       <c r="I3" s="3">
         <v>0.75</v>
@@ -759,7 +749,7 @@
         <v>2000</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
